--- a/frontend/apps/web/public/cbom_report.xlsx
+++ b/frontend/apps/web/public/cbom_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Domain</t>
   </si>
@@ -163,7 +163,7 @@
     <t>ML-KEM-768 (FIPS 203)</t>
   </si>
   <si>
-    <t>Plan migration of ECDHE-RSA to ML-KEM-768 (FIPS 203) before 2030 deprecation. Runway: 928 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
+    <t>Plan migration of ECDHE-RSA to ML-KEM-768 (FIPS 203) before 2030 deprecation. Runway: 919 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
   </si>
   <si>
     <t>www.pnb.bank.in</t>
@@ -202,7 +202,19 @@
     <t>ML-KEM-768 (FIPS 203) or X25519+ML-KEM hybrid</t>
   </si>
   <si>
-    <t>Plan migration of X25519 (TLS 1.3) to ML-KEM-768 (FIPS 203) or X25519+ML-KEM hybrid before 2035 disallowed cutoff. Runway: 3174 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
+    <t>Plan migration of X25519 (TLS 1.3) to ML-KEM-768 (FIPS 203) or X25519+ML-KEM hybrid before 2035 disallowed cutoff. Runway: 3165 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
+  </si>
+  <si>
+    <t>mbs.manipurrural.bank.in</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>cbdcr.pnbuat.bank.in</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
   </si>
 </sst>
 </file>
@@ -699,10 +711,10 @@
         <v>37</v>
       </c>
       <c r="L2">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="M2">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="N2" t="s">
         <v>38</v>
@@ -744,7 +756,7 @@
         <v>46</v>
       </c>
       <c r="AA2">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>47</v>
@@ -791,10 +803,10 @@
         <v>37</v>
       </c>
       <c r="L3">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="M3">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="N3" t="s">
         <v>38</v>
@@ -836,7 +848,7 @@
         <v>46</v>
       </c>
       <c r="AA3">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>47</v>
@@ -883,10 +895,10 @@
         <v>55</v>
       </c>
       <c r="L4">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="M4">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="N4" t="s">
         <v>56</v>
@@ -928,7 +940,7 @@
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>3174</v>
+        <v>3165</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>47</v>
@@ -937,6 +949,190 @@
         <v>61</v>
       </c>
       <c r="AD4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>2048</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5">
+        <v>156</v>
+      </c>
+      <c r="M5">
+        <v>208</v>
+      </c>
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5">
+        <v>10</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5" t="s">
+        <v>44</v>
+      </c>
+      <c r="U5" t="s">
+        <v>59</v>
+      </c>
+      <c r="V5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5">
+        <v>50</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA5">
+        <v>3165</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>2048</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6">
+        <v>147</v>
+      </c>
+      <c r="M6">
+        <v>217</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6">
+        <v>10</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
+        <v>44</v>
+      </c>
+      <c r="U6" t="s">
+        <v>59</v>
+      </c>
+      <c r="V6" t="s">
+        <v>42</v>
+      </c>
+      <c r="W6">
+        <v>50</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA6">
+        <v>3165</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD6" t="s">
         <v>62</v>
       </c>
     </row>

--- a/frontend/apps/web/public/cbom_report.xlsx
+++ b/frontend/apps/web/public/cbom_report.xlsx
@@ -163,7 +163,7 @@
     <t>ML-KEM-768 (FIPS 203)</t>
   </si>
   <si>
-    <t>Plan migration of ECDHE-RSA to ML-KEM-768 (FIPS 203) before 2030 deprecation. Runway: 919 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
+    <t>Plan migration of ECDHE-RSA to ML-KEM-768 (FIPS 203) before 2030 deprecation. Runway: 917 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
   </si>
   <si>
     <t>www.pnb.bank.in</t>
@@ -202,7 +202,7 @@
     <t>ML-KEM-768 (FIPS 203) or X25519+ML-KEM hybrid</t>
   </si>
   <si>
-    <t>Plan migration of X25519 (TLS 1.3) to ML-KEM-768 (FIPS 203) or X25519+ML-KEM hybrid before 2035 disallowed cutoff. Runway: 3165 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
+    <t>Plan migration of X25519 (TLS 1.3) to ML-KEM-768 (FIPS 203) or X25519+ML-KEM hybrid before 2035 disallowed cutoff. Runway: 3163 days. Ref: NIST IR 8547 ipd (Nov 2024), Table 4</t>
   </si>
   <si>
     <t>mbs.manipurrural.bank.in</t>
@@ -711,10 +711,10 @@
         <v>37</v>
       </c>
       <c r="L2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N2" t="s">
         <v>38</v>
@@ -756,7 +756,7 @@
         <v>46</v>
       </c>
       <c r="AA2">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>47</v>
@@ -803,10 +803,10 @@
         <v>37</v>
       </c>
       <c r="L3">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N3" t="s">
         <v>38</v>
@@ -848,7 +848,7 @@
         <v>46</v>
       </c>
       <c r="AA3">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>47</v>
@@ -895,10 +895,10 @@
         <v>55</v>
       </c>
       <c r="L4">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M4">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N4" t="s">
         <v>56</v>
@@ -940,7 +940,7 @@
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>47</v>
@@ -987,10 +987,10 @@
         <v>64</v>
       </c>
       <c r="L5">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M5">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N5" t="s">
         <v>56</v>
@@ -1032,7 +1032,7 @@
         <v>60</v>
       </c>
       <c r="AA5">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>47</v>
@@ -1079,10 +1079,10 @@
         <v>66</v>
       </c>
       <c r="L6">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="M6">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N6" t="s">
         <v>56</v>
@@ -1124,7 +1124,7 @@
         <v>60</v>
       </c>
       <c r="AA6">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>47</v>
